--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N51_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N51_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.33642083728324</v>
+        <v>5.417168386058526</v>
       </c>
       <c r="D2" t="n">
-        <v>13.57931220391924</v>
+        <v>2.206638233136877</v>
       </c>
       <c r="E2" t="n">
-        <v>10.66380846959406</v>
+        <v>1.732868876309034</v>
       </c>
       <c r="F2" t="n">
-        <v>9.913794984237684</v>
+        <v>1.610991684938624</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.36571889787077</v>
+        <v>6.396929320904</v>
       </c>
       <c r="D3" t="n">
-        <v>37.61695261223873</v>
+        <v>6.112754799488794</v>
       </c>
       <c r="E3" t="n">
-        <v>10.66380846959406</v>
+        <v>1.732868876309034</v>
       </c>
       <c r="F3" t="n">
-        <v>9.913794984237684</v>
+        <v>1.610991684938624</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.21041636788877</v>
+        <v>3.609192659781926</v>
       </c>
       <c r="D4" t="n">
-        <v>18.48036465153917</v>
+        <v>3.003059255875116</v>
       </c>
       <c r="E4" t="n">
-        <v>10.66380846959406</v>
+        <v>1.732868876309034</v>
       </c>
       <c r="F4" t="n">
-        <v>9.913794984237684</v>
+        <v>1.610991684938624</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.84897663056528</v>
+        <v>3.387958702466858</v>
       </c>
       <c r="D5" t="n">
-        <v>13.00585571213872</v>
+        <v>2.113451553222542</v>
       </c>
       <c r="E5" t="n">
-        <v>10.66380846959406</v>
+        <v>1.732868876309034</v>
       </c>
       <c r="F5" t="n">
-        <v>9.913794984237684</v>
+        <v>1.610991684938624</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>5.876577269888929</v>
+        <v>0.954943806356951</v>
       </c>
       <c r="D6" t="n">
-        <v>5.328888770148867</v>
+        <v>0.8659444251491908</v>
       </c>
       <c r="E6" t="n">
-        <v>10.66380846959406</v>
+        <v>1.732868876309034</v>
       </c>
       <c r="F6" t="n">
-        <v>9.913794984237684</v>
+        <v>1.610991684938624</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.68346867903955</v>
+        <v>3.198563660343928</v>
       </c>
       <c r="D7" t="n">
-        <v>16.91439534990763</v>
+        <v>2.74858924435999</v>
       </c>
       <c r="E7" t="n">
-        <v>10.66380846959406</v>
+        <v>1.732868876309034</v>
       </c>
       <c r="F7" t="n">
-        <v>9.913794984237684</v>
+        <v>1.610991684938624</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
